--- a/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Easthill_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Easthill_20260515.xlsx
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>23.75</v>
       </c>
       <c r="E9" t="n">
-        <v>47.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>10.25</v>
       </c>
       <c r="E13" t="n">
-        <v>10.25</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="14">
